--- a/artfynd/A 33783-2023 artfynd.xlsx
+++ b/artfynd/A 33783-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33783-2023 artfynd.xlsx
+++ b/artfynd/A 33783-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113169955</v>
+        <v>113168807</v>
       </c>
       <c r="B2" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558544</v>
+        <v>558535</v>
       </c>
       <c r="R2" t="n">
-        <v>6896893</v>
+        <v>6896887</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113168807</v>
+        <v>113168126</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558535</v>
+        <v>558545</v>
       </c>
       <c r="R3" t="n">
-        <v>6896887</v>
+        <v>6896895</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113168126</v>
+        <v>113169955</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558545</v>
+        <v>558544</v>
       </c>
       <c r="R4" t="n">
-        <v>6896895</v>
+        <v>6896893</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
